--- a/12629646.xlsx
+++ b/12629646.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="57">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -204,6 +204,9 @@
   </si>
   <si>
     <t>SEPTEMBER</t>
+  </si>
+  <si>
+    <t>Neutral</t>
   </si>
 </sst>
 </file>
@@ -1026,29 +1029,53 @@
       <c r="N6" s="12"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+      <c r="A7" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B7" s="14">
+        <v>120</v>
+      </c>
+      <c r="C7" s="14">
+        <v>0</v>
+      </c>
+      <c r="D7" s="14">
+        <v>60</v>
+      </c>
+      <c r="E7" s="14">
+        <v>60</v>
+      </c>
+      <c r="F7" s="14">
+        <v>250</v>
+      </c>
+      <c r="G7" s="14">
+        <v>5</v>
+      </c>
+      <c r="H7" s="14">
+        <v>30</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>520</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
+        <v>920</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N7" s="17"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="13"/>
+      <c r="A8" s="8">
+        <v>46282</v>
+      </c>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
@@ -1070,7 +1097,9 @@
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
+      <c r="A9" s="8">
+        <v>46283</v>
+      </c>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
@@ -1092,7 +1121,9 @@
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="13"/>
+      <c r="A10" s="8">
+        <v>46284</v>
+      </c>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
@@ -1114,7 +1145,9 @@
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
+      <c r="A11" s="8">
+        <v>46285</v>
+      </c>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
@@ -1136,7 +1169,9 @@
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
+      <c r="A12" s="8">
+        <v>46286</v>
+      </c>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
@@ -1158,7 +1193,9 @@
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
+      <c r="A13" s="8">
+        <v>46287</v>
+      </c>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
@@ -1180,7 +1217,9 @@
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
+      <c r="A14" s="8">
+        <v>46288</v>
+      </c>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
@@ -1202,7 +1241,9 @@
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
+      <c r="A15" s="8">
+        <v>46289</v>
+      </c>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
@@ -1224,7 +1265,9 @@
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
+      <c r="A16" s="8">
+        <v>46290</v>
+      </c>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
@@ -1246,7 +1289,9 @@
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="13"/>
+      <c r="A17" s="8">
+        <v>46291</v>
+      </c>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
@@ -1268,7 +1313,9 @@
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
+      <c r="A18" s="8">
+        <v>46292</v>
+      </c>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
@@ -1290,7 +1337,9 @@
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
+      <c r="A19" s="8">
+        <v>46293</v>
+      </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
@@ -1312,7 +1361,9 @@
       <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
+      <c r="A20" s="8">
+        <v>46294</v>
+      </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
@@ -1334,7 +1385,9 @@
       <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
+      <c r="A21" s="8">
+        <v>46295</v>
+      </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
       <c r="D21" s="14"/>

--- a/12629646.xlsx
+++ b/12629646.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -207,6 +207,12 @@
   </si>
   <si>
     <t>Neutral</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>High</t>
   </si>
 </sst>
 </file>
@@ -989,7 +995,7 @@
         <v>46280</v>
       </c>
       <c r="B6" s="9">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="C6" s="9">
         <v>0</v>
@@ -1011,11 +1017,11 @@
       </c>
       <c r="I6" s="10">
         <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
-        <v>405</v>
+        <v>945</v>
       </c>
       <c r="J6" s="10">
         <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
-        <v>1035</v>
+        <v>495</v>
       </c>
       <c r="K6" s="11" t="s">
         <v>49</v>
@@ -1033,7 +1039,7 @@
         <v>46281</v>
       </c>
       <c r="B7" s="14">
-        <v>120</v>
+        <v>600</v>
       </c>
       <c r="C7" s="14">
         <v>0</v>
@@ -1055,11 +1061,11 @@
       </c>
       <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v>520</v>
+        <v>1000</v>
       </c>
       <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v>920</v>
+        <v>440</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>49</v>
@@ -1076,48 +1082,88 @@
       <c r="A8" s="8">
         <v>46282</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="B8" s="14">
+        <v>600</v>
+      </c>
+      <c r="C8" s="14">
+        <v>0</v>
+      </c>
+      <c r="D8" s="14">
+        <v>45</v>
+      </c>
+      <c r="E8" s="14">
+        <v>90</v>
+      </c>
+      <c r="F8" s="14">
+        <v>150</v>
+      </c>
+      <c r="G8" s="14">
+        <v>3</v>
+      </c>
+      <c r="H8" s="14">
+        <v>60</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>945</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+        <v>495</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>46283</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="B9" s="14">
+        <v>600</v>
+      </c>
+      <c r="C9" s="14">
+        <v>0</v>
+      </c>
+      <c r="D9" s="14">
+        <v>120</v>
+      </c>
+      <c r="E9" s="14">
+        <v>60</v>
+      </c>
+      <c r="F9" s="14">
+        <v>300</v>
+      </c>
+      <c r="G9" s="14">
+        <v>6</v>
+      </c>
+      <c r="H9" s="14">
+        <v>60</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
+        <v>300</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">

--- a/12629646.xlsx
+++ b/12629646.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1170,24 +1170,44 @@
       <c r="A10" s="8">
         <v>46284</v>
       </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="B10" s="14">
+        <v>600</v>
+      </c>
+      <c r="C10" s="14">
+        <v>0</v>
+      </c>
+      <c r="D10" s="14">
+        <v>150</v>
+      </c>
+      <c r="E10" s="14">
+        <v>120</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14">
+        <v>240</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
+        <v>330</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">

--- a/12629646.xlsx
+++ b/12629646.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -213,6 +213,9 @@
   </si>
   <si>
     <t>High</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -1214,24 +1217,44 @@
       <c r="A11" s="8">
         <v>46285</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="B11" s="14">
+        <v>720</v>
+      </c>
+      <c r="C11" s="14">
+        <v>30</v>
+      </c>
+      <c r="D11" s="14">
+        <v>180</v>
+      </c>
+      <c r="E11" s="14">
+        <v>120</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>240</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
+        <v>150</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">

--- a/12629646.xlsx
+++ b/12629646.xlsx
@@ -1221,7 +1221,7 @@
         <v>720</v>
       </c>
       <c r="C11" s="14">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D11" s="14">
         <v>180</v>
@@ -1240,11 +1240,11 @@
       </c>
       <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v>1290</v>
+        <v>1305</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="K11" s="16" t="s">
         <v>56</v>

--- a/12629646.xlsx
+++ b/12629646.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1261,24 +1261,44 @@
       <c r="A12" s="8">
         <v>46286</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="B12" s="14">
+        <v>600</v>
+      </c>
+      <c r="C12" s="14">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14">
+        <v>150</v>
+      </c>
+      <c r="E12" s="14">
+        <v>180</v>
+      </c>
+      <c r="F12" s="14">
+        <v>200</v>
+      </c>
+      <c r="G12" s="14">
+        <v>4</v>
+      </c>
+      <c r="H12" s="14">
+        <v>180</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
+        <v>130</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">

--- a/12629646.xlsx
+++ b/12629646.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1305,24 +1305,44 @@
       <c r="A13" s="8">
         <v>46287</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="B13" s="14">
+        <v>600</v>
+      </c>
+      <c r="C13" s="14">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14">
+        <v>120</v>
+      </c>
+      <c r="E13" s="14">
+        <v>240</v>
+      </c>
+      <c r="F13" s="14">
+        <v>250</v>
+      </c>
+      <c r="G13" s="14">
+        <v>5</v>
+      </c>
+      <c r="H13" s="14">
+        <v>120</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
+        <v>110</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">

--- a/12629646.xlsx
+++ b/12629646.xlsx
@@ -1324,15 +1324,15 @@
         <v>5</v>
       </c>
       <c r="H13" s="14">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v>1330</v>
+        <v>1360</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>56</v>

--- a/12629646.xlsx
+++ b/12629646.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1349,24 +1349,44 @@
       <c r="A14" s="8">
         <v>46288</v>
       </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="B14" s="14">
+        <v>660</v>
+      </c>
+      <c r="C14" s="14">
+        <v>0</v>
+      </c>
+      <c r="D14" s="14">
+        <v>90</v>
+      </c>
+      <c r="E14" s="14">
+        <v>150</v>
+      </c>
+      <c r="F14" s="14">
+        <v>250</v>
+      </c>
+      <c r="G14" s="14">
+        <v>5</v>
+      </c>
+      <c r="H14" s="14">
+        <v>120</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
+        <v>170</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">

--- a/12629646.xlsx
+++ b/12629646.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1393,24 +1393,44 @@
       <c r="A15" s="8">
         <v>46289</v>
       </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="B15" s="14">
+        <v>660</v>
+      </c>
+      <c r="C15" s="14">
+        <v>0</v>
+      </c>
+      <c r="D15" s="14">
+        <v>100</v>
+      </c>
+      <c r="E15" s="14">
+        <v>240</v>
+      </c>
+      <c r="F15" s="14">
+        <v>100</v>
+      </c>
+      <c r="G15" s="14">
+        <v>2</v>
+      </c>
+      <c r="H15" s="14">
+        <v>150</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
+        <v>190</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">

--- a/12629646.xlsx
+++ b/12629646.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1437,24 +1437,44 @@
       <c r="A16" s="8">
         <v>46290</v>
       </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="B16" s="14">
+        <v>630</v>
+      </c>
+      <c r="C16" s="14">
+        <v>0</v>
+      </c>
+      <c r="D16" s="14">
+        <v>120</v>
+      </c>
+      <c r="E16" s="14">
+        <v>150</v>
+      </c>
+      <c r="F16" s="14">
+        <v>300</v>
+      </c>
+      <c r="G16" s="14">
+        <v>6</v>
+      </c>
+      <c r="H16" s="14">
+        <v>120</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
+        <v>120</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">

--- a/12629646.xlsx
+++ b/12629646.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -216,6 +216,12 @@
   </si>
   <si>
     <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
   </si>
 </sst>
 </file>
@@ -1481,24 +1487,44 @@
       <c r="A17" s="8">
         <v>46291</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="B17" s="14">
+        <v>600</v>
+      </c>
+      <c r="C17" s="14">
+        <v>60</v>
+      </c>
+      <c r="D17" s="14">
+        <v>60</v>
+      </c>
+      <c r="E17" s="14">
+        <v>240</v>
+      </c>
+      <c r="F17" s="14">
+        <v>150</v>
+      </c>
+      <c r="G17" s="14">
+        <v>3</v>
+      </c>
+      <c r="H17" s="14">
+        <v>180</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
+        <v>150</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
